--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0002T0006Z000C1N64_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0002T0006Z000C1N64_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>35.394873773163</v>
+        <v>5.751666988138988</v>
       </c>
       <c r="D2" t="n">
-        <v>36.22370979096617</v>
+        <v>5.886352841032003</v>
       </c>
       <c r="E2" t="n">
-        <v>19.10749733281182</v>
+        <v>3.104968316581921</v>
       </c>
       <c r="F2" t="n">
-        <v>4.848230410834262</v>
+        <v>0.7878374417605676</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>32.58499678478022</v>
+        <v>5.295061977526785</v>
       </c>
       <c r="D3" t="n">
-        <v>29.21566550627105</v>
+        <v>4.747545644769047</v>
       </c>
       <c r="E3" t="n">
-        <v>19.10749733281182</v>
+        <v>3.104968316581921</v>
       </c>
       <c r="F3" t="n">
-        <v>4.848230410834262</v>
+        <v>0.7878374417605676</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>39.22990292414695</v>
+        <v>6.374859225173879</v>
       </c>
       <c r="D4" t="n">
-        <v>21.5187639381033</v>
+        <v>3.496799139941786</v>
       </c>
       <c r="E4" t="n">
-        <v>19.10749733281182</v>
+        <v>3.104968316581921</v>
       </c>
       <c r="F4" t="n">
-        <v>4.848230410834262</v>
+        <v>0.7878374417605676</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>25.53606920140299</v>
+        <v>4.149611245227987</v>
       </c>
       <c r="D5" t="n">
-        <v>27.52846765660392</v>
+        <v>4.473375994198138</v>
       </c>
       <c r="E5" t="n">
-        <v>19.10749733281182</v>
+        <v>3.104968316581921</v>
       </c>
       <c r="F5" t="n">
-        <v>4.848230410834262</v>
+        <v>0.7878374417605676</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>72.98266641582427</v>
+        <v>11.85968329257144</v>
       </c>
       <c r="D6" t="n">
-        <v>29.79591379830774</v>
+        <v>4.841835992225008</v>
       </c>
       <c r="E6" t="n">
-        <v>19.10749733281182</v>
+        <v>3.104968316581921</v>
       </c>
       <c r="F6" t="n">
-        <v>4.848230410834262</v>
+        <v>0.7878374417605676</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>72.57749085154515</v>
+        <v>11.79384226337609</v>
       </c>
       <c r="D7" t="n">
-        <v>22.84264913174753</v>
+        <v>3.711930483908974</v>
       </c>
       <c r="E7" t="n">
-        <v>19.10749733281182</v>
+        <v>3.104968316581921</v>
       </c>
       <c r="F7" t="n">
-        <v>4.848230410834262</v>
+        <v>0.7878374417605676</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
